--- a/002-board-game-nights/board-game-nights-quote.xlsx
+++ b/002-board-game-nights/board-game-nights-quote.xlsx
@@ -1,22 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arut/repo/mscac-event-proposals-2026:27/002-board-game-nights/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4AB79F-A185-AD43-8EFC-D09C10F549D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="240" yWindow="500" windowWidth="33360" windowHeight="18760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="32">
   <si>
     <t>Cosmic Pizza</t>
   </si>
@@ -42,16 +61,10 @@
     <t>Chicken Delight Pizza (18Inch)</t>
   </si>
   <si>
-    <t>https://collegestreet.restaurantsolutions.ca/,</t>
-  </si>
-  <si>
     <t>Non Veg (Tandoori Chicken, Onions, Jalapeno Peppers &amp; Mozzarella Cheese)</t>
   </si>
   <si>
     <t>Classic Vegetarian Pizza (18Inch)</t>
-  </si>
-  <si>
-    <t>Serves - 4or5</t>
   </si>
   <si>
     <t>Veg (Onions, Mushrooms, Green Peppers, Cooked Tomatoes &amp; Mozzarella Cheese)</t>
@@ -68,12 +81,64 @@
   <si>
     <t xml:space="preserve">Total </t>
   </si>
+  <si>
+    <t>Fresca Pizza and Pasta</t>
+  </si>
+  <si>
+    <t>Veg (Mushroom, green pepper, onions, tomatoes, extra cheese.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pop </t>
+  </si>
+  <si>
+    <t>Each served 3</t>
+  </si>
+  <si>
+    <t>Serves - 4-5</t>
+  </si>
+  <si>
+    <t>Pizza Nova</t>
+  </si>
+  <si>
+    <t>Party - Canadian</t>
+  </si>
+  <si>
+    <t>Party - Veggie</t>
+  </si>
+  <si>
+    <t>Serves 4</t>
+  </si>
+  <si>
+    <t>https://pizzanova.com/products/drinks</t>
+  </si>
+  <si>
+    <t>Non Veg (
+Regular Dough, Tomato Sauce, Mozzarella, Pepperoni, Bacon, Fresh Mushrooms)</t>
+  </si>
+  <si>
+    <t>Veg (Regular Dough, Tomato Sauce, Mozzarella, Green Peppers, Fresh Mushrooms, Spanish Onions)</t>
+  </si>
+  <si>
+    <t>CANADIAN SPECIAL</t>
+  </si>
+  <si>
+    <t>Non Veg (Mozzarella cheese, bacon, ham, ground beef, pepperoni, mushrooms and Italian hot sausage.)</t>
+  </si>
+  <si>
+    <t>ARRABBIATA (18")</t>
+  </si>
+  <si>
+    <t>https://www.kingslice.ca/menu?location=Bloor+Street+West&amp;menu=pizza</t>
+  </si>
+  <si>
+    <t>https://collegestreet.restaurantsolutions.ca/</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="3">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -94,6 +159,27 @@
       <name val="PingFang"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color rgb="FF1F2326"/>
+      <name val="PingFang"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -112,10 +198,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -123,19 +210,40 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -173,7 +281,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -207,6 +315,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -241,9 +350,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -416,113 +526,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:CV100"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" customWidth="1"/>
-    <col min="5" max="5" width="17.85546875" customWidth="1"/>
-    <col min="6" max="6" width="17.85546875" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" customWidth="1"/>
-    <col min="11" max="11" width="10.85546875" customWidth="1"/>
-    <col min="12" max="12" width="10.85546875" customWidth="1"/>
-    <col min="13" max="13" width="10.85546875" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" customWidth="1"/>
-    <col min="15" max="15" width="10.85546875" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" customWidth="1"/>
-    <col min="17" max="17" width="10.85546875" customWidth="1"/>
-    <col min="18" max="18" width="10.85546875" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" customWidth="1"/>
-    <col min="21" max="21" width="10.85546875" customWidth="1"/>
-    <col min="22" max="22" width="10.85546875" customWidth="1"/>
-    <col min="23" max="23" width="10.85546875" customWidth="1"/>
-    <col min="24" max="24" width="10.85546875" customWidth="1"/>
-    <col min="25" max="25" width="10.85546875" customWidth="1"/>
-    <col min="26" max="26" width="10.85546875" customWidth="1"/>
-    <col min="27" max="27" width="10.85546875" customWidth="1"/>
-    <col min="28" max="28" width="10.85546875" customWidth="1"/>
-    <col min="29" max="29" width="10.85546875" customWidth="1"/>
-    <col min="30" max="30" width="10.85546875" customWidth="1"/>
-    <col min="31" max="31" width="10.85546875" customWidth="1"/>
-    <col min="32" max="32" width="10.85546875" customWidth="1"/>
-    <col min="33" max="33" width="10.85546875" customWidth="1"/>
-    <col min="34" max="34" width="10.85546875" customWidth="1"/>
-    <col min="35" max="35" width="10.85546875" customWidth="1"/>
-    <col min="36" max="36" width="10.85546875" customWidth="1"/>
-    <col min="37" max="37" width="10.85546875" customWidth="1"/>
-    <col min="38" max="38" width="10.85546875" customWidth="1"/>
-    <col min="39" max="39" width="10.85546875" customWidth="1"/>
-    <col min="40" max="40" width="10.85546875" customWidth="1"/>
-    <col min="41" max="41" width="10.85546875" customWidth="1"/>
-    <col min="42" max="42" width="10.85546875" customWidth="1"/>
-    <col min="43" max="43" width="10.85546875" customWidth="1"/>
-    <col min="44" max="44" width="10.85546875" customWidth="1"/>
-    <col min="45" max="45" width="10.85546875" customWidth="1"/>
-    <col min="46" max="46" width="10.85546875" customWidth="1"/>
-    <col min="47" max="47" width="10.85546875" customWidth="1"/>
-    <col min="48" max="48" width="10.85546875" customWidth="1"/>
-    <col min="49" max="49" width="10.85546875" customWidth="1"/>
-    <col min="50" max="50" width="10.85546875" customWidth="1"/>
-    <col min="51" max="51" width="10.85546875" customWidth="1"/>
-    <col min="52" max="52" width="10.85546875" customWidth="1"/>
-    <col min="53" max="53" width="10.85546875" customWidth="1"/>
-    <col min="54" max="54" width="10.85546875" customWidth="1"/>
-    <col min="55" max="55" width="10.85546875" customWidth="1"/>
-    <col min="56" max="56" width="10.85546875" customWidth="1"/>
-    <col min="57" max="57" width="10.85546875" customWidth="1"/>
-    <col min="58" max="58" width="10.85546875" customWidth="1"/>
-    <col min="59" max="59" width="10.85546875" customWidth="1"/>
-    <col min="60" max="60" width="10.85546875" customWidth="1"/>
-    <col min="61" max="61" width="10.85546875" customWidth="1"/>
-    <col min="62" max="62" width="10.85546875" customWidth="1"/>
-    <col min="63" max="63" width="10.85546875" customWidth="1"/>
-    <col min="64" max="64" width="10.85546875" customWidth="1"/>
-    <col min="65" max="65" width="10.85546875" customWidth="1"/>
-    <col min="66" max="66" width="10.85546875" customWidth="1"/>
-    <col min="67" max="67" width="10.85546875" customWidth="1"/>
-    <col min="68" max="68" width="10.85546875" customWidth="1"/>
-    <col min="69" max="69" width="10.85546875" customWidth="1"/>
-    <col min="70" max="70" width="10.85546875" customWidth="1"/>
-    <col min="71" max="71" width="10.85546875" customWidth="1"/>
-    <col min="72" max="72" width="10.85546875" customWidth="1"/>
-    <col min="73" max="73" width="10.85546875" customWidth="1"/>
-    <col min="74" max="74" width="10.85546875" customWidth="1"/>
-    <col min="75" max="75" width="10.85546875" customWidth="1"/>
-    <col min="76" max="76" width="10.85546875" customWidth="1"/>
-    <col min="77" max="77" width="10.85546875" customWidth="1"/>
-    <col min="78" max="78" width="10.85546875" customWidth="1"/>
-    <col min="79" max="79" width="10.85546875" customWidth="1"/>
-    <col min="80" max="80" width="10.85546875" customWidth="1"/>
-    <col min="81" max="81" width="10.85546875" customWidth="1"/>
-    <col min="82" max="82" width="10.85546875" customWidth="1"/>
-    <col min="83" max="83" width="10.85546875" customWidth="1"/>
-    <col min="84" max="84" width="10.85546875" customWidth="1"/>
-    <col min="85" max="85" width="10.85546875" customWidth="1"/>
-    <col min="86" max="86" width="10.85546875" customWidth="1"/>
-    <col min="87" max="87" width="10.85546875" customWidth="1"/>
-    <col min="88" max="88" width="10.85546875" customWidth="1"/>
-    <col min="89" max="89" width="10.85546875" customWidth="1"/>
-    <col min="90" max="90" width="10.85546875" customWidth="1"/>
-    <col min="91" max="91" width="10.85546875" customWidth="1"/>
-    <col min="92" max="92" width="10.85546875" customWidth="1"/>
-    <col min="93" max="93" width="10.85546875" customWidth="1"/>
-    <col min="94" max="94" width="10.85546875" customWidth="1"/>
-    <col min="95" max="95" width="10.85546875" customWidth="1"/>
-    <col min="96" max="96" width="10.85546875" customWidth="1"/>
-    <col min="97" max="97" width="10.85546875" customWidth="1"/>
-    <col min="98" max="98" width="10.85546875" customWidth="1"/>
-    <col min="99" max="99" width="10.85546875" customWidth="1"/>
-    <col min="100" max="100" width="10.85546875" customWidth="1"/>
+    <col min="2" max="4" width="10.83203125" customWidth="1"/>
+    <col min="5" max="6" width="17.83203125" customWidth="1"/>
+    <col min="7" max="7" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.1640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13.1640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="10.83203125" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="100" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:100" ht="27" customHeight="1">
+    <row r="1" spans="1:100" ht="28" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -531,13 +553,17 @@
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
+      <c r="G1" s="3" t="s">
+        <v>15</v>
+      </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
+      <c r="M1" s="3" t="s">
+        <v>20</v>
+      </c>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
@@ -645,18 +671,42 @@
       <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
+      <c r="G2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>6</v>
+      </c>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
@@ -740,7 +790,7 @@
       <c r="CU2" s="2"/>
       <c r="CV2" s="2"/>
     </row>
-    <row r="3" spans="1:100" ht="135.75" customHeight="1">
+    <row r="3" spans="1:100" ht="231">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -750,28 +800,54 @@
       <c r="C3" s="2">
         <v>2</v>
       </c>
-      <c r="D3" s="2" t="str">
+      <c r="D3" s="2">
         <f>B3*C3</f>
         <v>69.98</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>9</v>
+      <c r="G3" s="4" t="s">
+        <v>27</v>
       </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
+      <c r="H3" s="5">
+        <v>28.25</v>
+      </c>
+      <c r="I3" s="2">
+        <v>3</v>
+      </c>
+      <c r="J3" s="2">
+        <f>H3*I3</f>
+        <v>84.75</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="N3" s="2">
+        <v>38.94</v>
+      </c>
+      <c r="O3" s="2">
+        <v>2</v>
+      </c>
+      <c r="P3" s="2">
+        <f>N3*O3</f>
+        <v>77.88</v>
+      </c>
+      <c r="Q3" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>25</v>
+      </c>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
@@ -857,7 +933,7 @@
     </row>
     <row r="4" spans="1:100" ht="135.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4" s="2">
         <v>34.99</v>
@@ -865,28 +941,54 @@
       <c r="C4" s="2">
         <v>2</v>
       </c>
-      <c r="D4" s="2" t="str">
+      <c r="D4" s="2">
         <f>B4*C4</f>
         <v>69.98</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
+      <c r="G4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="5">
+        <v>28.25</v>
+      </c>
+      <c r="I4" s="2">
+        <v>3</v>
+      </c>
+      <c r="J4" s="2">
+        <f>H4*I4</f>
+        <v>84.75</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="N4" s="2">
+        <v>38.090000000000003</v>
+      </c>
+      <c r="O4" s="2">
+        <v>2</v>
+      </c>
+      <c r="P4" s="2">
+        <f>N4*O4</f>
+        <v>76.180000000000007</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
@@ -972,7 +1074,7 @@
     </row>
     <row r="5" spans="1:100" ht="27" customHeight="1">
       <c r="A5" s="2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2">
         <v>2.25</v>
@@ -980,26 +1082,49 @@
       <c r="C5" s="2">
         <v>20</v>
       </c>
-      <c r="D5" s="2" t="str">
+      <c r="D5" s="2">
         <f>B5*C5</f>
         <v>45</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
+      <c r="G5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1.25</v>
+      </c>
+      <c r="I5" s="2">
+        <f>20</f>
+        <v>20</v>
+      </c>
+      <c r="J5" s="2">
+        <f>H5*I5</f>
+        <v>25</v>
+      </c>
       <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
+      <c r="L5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="N5" s="2">
+        <v>1.99</v>
+      </c>
+      <c r="O5" s="2">
+        <v>20</v>
+      </c>
+      <c r="P5" s="2">
+        <f>N5*O5</f>
+        <v>39.799999999999997</v>
+      </c>
       <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
+      <c r="R5" s="2" t="s">
+        <v>12</v>
+      </c>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
@@ -1085,7 +1210,7 @@
     </row>
     <row r="6" spans="1:100" ht="34.5" customHeight="1">
       <c r="A6" s="2" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="2">
         <v>20</v>
@@ -1093,22 +1218,42 @@
       <c r="C6" s="2">
         <v>1</v>
       </c>
-      <c r="D6" s="2" t="str">
+      <c r="D6" s="2">
         <f>B6*C6+D7+D7</f>
         <v>20</v>
       </c>
       <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
+      <c r="G6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="2">
+        <v>20</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2">
+        <f>H6*I6+I7+I7</f>
+        <v>20</v>
+      </c>
       <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
+      <c r="L6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M6" s="2">
+        <v>20</v>
+      </c>
+      <c r="N6" s="2">
+        <v>1</v>
+      </c>
+      <c r="O6" s="2">
+        <f>M6*N6+O7+O7</f>
+        <v>20</v>
+      </c>
+      <c r="P6" s="2">
+        <f>O6*N6</f>
+        <v>20</v>
+      </c>
       <c r="Q6" s="2"/>
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
@@ -1400,26 +1545,36 @@
     </row>
     <row r="9" spans="1:100" ht="27" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
-      <c r="D9" s="2" t="str">
+      <c r="D9" s="2">
         <f>SUM(D3:D8)</f>
         <v>204.96</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
+      <c r="G9" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
+      <c r="J9" s="2">
+        <f>SUM(J3:J6)</f>
+        <v>214.5</v>
+      </c>
       <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
+      <c r="L9" s="2" t="s">
+        <v>4</v>
+      </c>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
+      <c r="P9" s="2">
+        <f>SUM(P3:P6)</f>
+        <v>213.86</v>
+      </c>
       <c r="Q9" s="2"/>
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
@@ -10788,115 +10943,21 @@
       <c r="CV100" s="2"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="Q3" r:id="rId1" xr:uid="{110E2199-DBC2-DA4E-A972-BA895550E106}"/>
+    <hyperlink ref="K3" r:id="rId2" xr:uid="{080C8070-31B2-7F4C-A586-4FCDAD5776EE}"/>
+    <hyperlink ref="E3" r:id="rId3" xr:uid="{0884733D-ACAA-3444-A1C8-681B7F3DFD8D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:CV100"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" customWidth="1"/>
-    <col min="11" max="11" width="10.85546875" customWidth="1"/>
-    <col min="12" max="12" width="10.85546875" customWidth="1"/>
-    <col min="13" max="13" width="10.85546875" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" customWidth="1"/>
-    <col min="15" max="15" width="10.85546875" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" customWidth="1"/>
-    <col min="17" max="17" width="10.85546875" customWidth="1"/>
-    <col min="18" max="18" width="10.85546875" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" customWidth="1"/>
-    <col min="21" max="21" width="10.85546875" customWidth="1"/>
-    <col min="22" max="22" width="10.85546875" customWidth="1"/>
-    <col min="23" max="23" width="10.85546875" customWidth="1"/>
-    <col min="24" max="24" width="10.85546875" customWidth="1"/>
-    <col min="25" max="25" width="10.85546875" customWidth="1"/>
-    <col min="26" max="26" width="10.85546875" customWidth="1"/>
-    <col min="27" max="27" width="10.85546875" customWidth="1"/>
-    <col min="28" max="28" width="10.85546875" customWidth="1"/>
-    <col min="29" max="29" width="10.85546875" customWidth="1"/>
-    <col min="30" max="30" width="10.85546875" customWidth="1"/>
-    <col min="31" max="31" width="10.85546875" customWidth="1"/>
-    <col min="32" max="32" width="10.85546875" customWidth="1"/>
-    <col min="33" max="33" width="10.85546875" customWidth="1"/>
-    <col min="34" max="34" width="10.85546875" customWidth="1"/>
-    <col min="35" max="35" width="10.85546875" customWidth="1"/>
-    <col min="36" max="36" width="10.85546875" customWidth="1"/>
-    <col min="37" max="37" width="10.85546875" customWidth="1"/>
-    <col min="38" max="38" width="10.85546875" customWidth="1"/>
-    <col min="39" max="39" width="10.85546875" customWidth="1"/>
-    <col min="40" max="40" width="10.85546875" customWidth="1"/>
-    <col min="41" max="41" width="10.85546875" customWidth="1"/>
-    <col min="42" max="42" width="10.85546875" customWidth="1"/>
-    <col min="43" max="43" width="10.85546875" customWidth="1"/>
-    <col min="44" max="44" width="10.85546875" customWidth="1"/>
-    <col min="45" max="45" width="10.85546875" customWidth="1"/>
-    <col min="46" max="46" width="10.85546875" customWidth="1"/>
-    <col min="47" max="47" width="10.85546875" customWidth="1"/>
-    <col min="48" max="48" width="10.85546875" customWidth="1"/>
-    <col min="49" max="49" width="10.85546875" customWidth="1"/>
-    <col min="50" max="50" width="10.85546875" customWidth="1"/>
-    <col min="51" max="51" width="10.85546875" customWidth="1"/>
-    <col min="52" max="52" width="10.85546875" customWidth="1"/>
-    <col min="53" max="53" width="10.85546875" customWidth="1"/>
-    <col min="54" max="54" width="10.85546875" customWidth="1"/>
-    <col min="55" max="55" width="10.85546875" customWidth="1"/>
-    <col min="56" max="56" width="10.85546875" customWidth="1"/>
-    <col min="57" max="57" width="10.85546875" customWidth="1"/>
-    <col min="58" max="58" width="10.85546875" customWidth="1"/>
-    <col min="59" max="59" width="10.85546875" customWidth="1"/>
-    <col min="60" max="60" width="10.85546875" customWidth="1"/>
-    <col min="61" max="61" width="10.85546875" customWidth="1"/>
-    <col min="62" max="62" width="10.85546875" customWidth="1"/>
-    <col min="63" max="63" width="10.85546875" customWidth="1"/>
-    <col min="64" max="64" width="10.85546875" customWidth="1"/>
-    <col min="65" max="65" width="10.85546875" customWidth="1"/>
-    <col min="66" max="66" width="10.85546875" customWidth="1"/>
-    <col min="67" max="67" width="10.85546875" customWidth="1"/>
-    <col min="68" max="68" width="10.85546875" customWidth="1"/>
-    <col min="69" max="69" width="10.85546875" customWidth="1"/>
-    <col min="70" max="70" width="10.85546875" customWidth="1"/>
-    <col min="71" max="71" width="10.85546875" customWidth="1"/>
-    <col min="72" max="72" width="10.85546875" customWidth="1"/>
-    <col min="73" max="73" width="10.85546875" customWidth="1"/>
-    <col min="74" max="74" width="10.85546875" customWidth="1"/>
-    <col min="75" max="75" width="10.85546875" customWidth="1"/>
-    <col min="76" max="76" width="10.85546875" customWidth="1"/>
-    <col min="77" max="77" width="10.85546875" customWidth="1"/>
-    <col min="78" max="78" width="10.85546875" customWidth="1"/>
-    <col min="79" max="79" width="10.85546875" customWidth="1"/>
-    <col min="80" max="80" width="10.85546875" customWidth="1"/>
-    <col min="81" max="81" width="10.85546875" customWidth="1"/>
-    <col min="82" max="82" width="10.85546875" customWidth="1"/>
-    <col min="83" max="83" width="10.85546875" customWidth="1"/>
-    <col min="84" max="84" width="10.85546875" customWidth="1"/>
-    <col min="85" max="85" width="10.85546875" customWidth="1"/>
-    <col min="86" max="86" width="10.85546875" customWidth="1"/>
-    <col min="87" max="87" width="10.85546875" customWidth="1"/>
-    <col min="88" max="88" width="10.85546875" customWidth="1"/>
-    <col min="89" max="89" width="10.85546875" customWidth="1"/>
-    <col min="90" max="90" width="10.85546875" customWidth="1"/>
-    <col min="91" max="91" width="10.85546875" customWidth="1"/>
-    <col min="92" max="92" width="10.85546875" customWidth="1"/>
-    <col min="93" max="93" width="10.85546875" customWidth="1"/>
-    <col min="94" max="94" width="10.85546875" customWidth="1"/>
-    <col min="95" max="95" width="10.85546875" customWidth="1"/>
-    <col min="96" max="96" width="10.85546875" customWidth="1"/>
-    <col min="97" max="97" width="10.85546875" customWidth="1"/>
-    <col min="98" max="98" width="10.85546875" customWidth="1"/>
-    <col min="99" max="99" width="10.85546875" customWidth="1"/>
-    <col min="100" max="100" width="10.85546875" customWidth="1"/>
+    <col min="1" max="100" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:100" ht="27" customHeight="1">
@@ -21105,110 +21166,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:CV100"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" customWidth="1"/>
-    <col min="3" max="3" width="10.85546875" customWidth="1"/>
-    <col min="4" max="4" width="10.85546875" customWidth="1"/>
-    <col min="5" max="5" width="10.85546875" customWidth="1"/>
-    <col min="6" max="6" width="10.85546875" customWidth="1"/>
-    <col min="7" max="7" width="10.85546875" customWidth="1"/>
-    <col min="8" max="8" width="10.85546875" customWidth="1"/>
-    <col min="9" max="9" width="10.85546875" customWidth="1"/>
-    <col min="10" max="10" width="10.85546875" customWidth="1"/>
-    <col min="11" max="11" width="10.85546875" customWidth="1"/>
-    <col min="12" max="12" width="10.85546875" customWidth="1"/>
-    <col min="13" max="13" width="10.85546875" customWidth="1"/>
-    <col min="14" max="14" width="10.85546875" customWidth="1"/>
-    <col min="15" max="15" width="10.85546875" customWidth="1"/>
-    <col min="16" max="16" width="10.85546875" customWidth="1"/>
-    <col min="17" max="17" width="10.85546875" customWidth="1"/>
-    <col min="18" max="18" width="10.85546875" customWidth="1"/>
-    <col min="19" max="19" width="10.85546875" customWidth="1"/>
-    <col min="20" max="20" width="10.85546875" customWidth="1"/>
-    <col min="21" max="21" width="10.85546875" customWidth="1"/>
-    <col min="22" max="22" width="10.85546875" customWidth="1"/>
-    <col min="23" max="23" width="10.85546875" customWidth="1"/>
-    <col min="24" max="24" width="10.85546875" customWidth="1"/>
-    <col min="25" max="25" width="10.85546875" customWidth="1"/>
-    <col min="26" max="26" width="10.85546875" customWidth="1"/>
-    <col min="27" max="27" width="10.85546875" customWidth="1"/>
-    <col min="28" max="28" width="10.85546875" customWidth="1"/>
-    <col min="29" max="29" width="10.85546875" customWidth="1"/>
-    <col min="30" max="30" width="10.85546875" customWidth="1"/>
-    <col min="31" max="31" width="10.85546875" customWidth="1"/>
-    <col min="32" max="32" width="10.85546875" customWidth="1"/>
-    <col min="33" max="33" width="10.85546875" customWidth="1"/>
-    <col min="34" max="34" width="10.85546875" customWidth="1"/>
-    <col min="35" max="35" width="10.85546875" customWidth="1"/>
-    <col min="36" max="36" width="10.85546875" customWidth="1"/>
-    <col min="37" max="37" width="10.85546875" customWidth="1"/>
-    <col min="38" max="38" width="10.85546875" customWidth="1"/>
-    <col min="39" max="39" width="10.85546875" customWidth="1"/>
-    <col min="40" max="40" width="10.85546875" customWidth="1"/>
-    <col min="41" max="41" width="10.85546875" customWidth="1"/>
-    <col min="42" max="42" width="10.85546875" customWidth="1"/>
-    <col min="43" max="43" width="10.85546875" customWidth="1"/>
-    <col min="44" max="44" width="10.85546875" customWidth="1"/>
-    <col min="45" max="45" width="10.85546875" customWidth="1"/>
-    <col min="46" max="46" width="10.85546875" customWidth="1"/>
-    <col min="47" max="47" width="10.85546875" customWidth="1"/>
-    <col min="48" max="48" width="10.85546875" customWidth="1"/>
-    <col min="49" max="49" width="10.85546875" customWidth="1"/>
-    <col min="50" max="50" width="10.85546875" customWidth="1"/>
-    <col min="51" max="51" width="10.85546875" customWidth="1"/>
-    <col min="52" max="52" width="10.85546875" customWidth="1"/>
-    <col min="53" max="53" width="10.85546875" customWidth="1"/>
-    <col min="54" max="54" width="10.85546875" customWidth="1"/>
-    <col min="55" max="55" width="10.85546875" customWidth="1"/>
-    <col min="56" max="56" width="10.85546875" customWidth="1"/>
-    <col min="57" max="57" width="10.85546875" customWidth="1"/>
-    <col min="58" max="58" width="10.85546875" customWidth="1"/>
-    <col min="59" max="59" width="10.85546875" customWidth="1"/>
-    <col min="60" max="60" width="10.85546875" customWidth="1"/>
-    <col min="61" max="61" width="10.85546875" customWidth="1"/>
-    <col min="62" max="62" width="10.85546875" customWidth="1"/>
-    <col min="63" max="63" width="10.85546875" customWidth="1"/>
-    <col min="64" max="64" width="10.85546875" customWidth="1"/>
-    <col min="65" max="65" width="10.85546875" customWidth="1"/>
-    <col min="66" max="66" width="10.85546875" customWidth="1"/>
-    <col min="67" max="67" width="10.85546875" customWidth="1"/>
-    <col min="68" max="68" width="10.85546875" customWidth="1"/>
-    <col min="69" max="69" width="10.85546875" customWidth="1"/>
-    <col min="70" max="70" width="10.85546875" customWidth="1"/>
-    <col min="71" max="71" width="10.85546875" customWidth="1"/>
-    <col min="72" max="72" width="10.85546875" customWidth="1"/>
-    <col min="73" max="73" width="10.85546875" customWidth="1"/>
-    <col min="74" max="74" width="10.85546875" customWidth="1"/>
-    <col min="75" max="75" width="10.85546875" customWidth="1"/>
-    <col min="76" max="76" width="10.85546875" customWidth="1"/>
-    <col min="77" max="77" width="10.85546875" customWidth="1"/>
-    <col min="78" max="78" width="10.85546875" customWidth="1"/>
-    <col min="79" max="79" width="10.85546875" customWidth="1"/>
-    <col min="80" max="80" width="10.85546875" customWidth="1"/>
-    <col min="81" max="81" width="10.85546875" customWidth="1"/>
-    <col min="82" max="82" width="10.85546875" customWidth="1"/>
-    <col min="83" max="83" width="10.85546875" customWidth="1"/>
-    <col min="84" max="84" width="10.85546875" customWidth="1"/>
-    <col min="85" max="85" width="10.85546875" customWidth="1"/>
-    <col min="86" max="86" width="10.85546875" customWidth="1"/>
-    <col min="87" max="87" width="10.85546875" customWidth="1"/>
-    <col min="88" max="88" width="10.85546875" customWidth="1"/>
-    <col min="89" max="89" width="10.85546875" customWidth="1"/>
-    <col min="90" max="90" width="10.85546875" customWidth="1"/>
-    <col min="91" max="91" width="10.85546875" customWidth="1"/>
-    <col min="92" max="92" width="10.85546875" customWidth="1"/>
-    <col min="93" max="93" width="10.85546875" customWidth="1"/>
-    <col min="94" max="94" width="10.85546875" customWidth="1"/>
-    <col min="95" max="95" width="10.85546875" customWidth="1"/>
-    <col min="96" max="96" width="10.85546875" customWidth="1"/>
-    <col min="97" max="97" width="10.85546875" customWidth="1"/>
-    <col min="98" max="98" width="10.85546875" customWidth="1"/>
-    <col min="99" max="99" width="10.85546875" customWidth="1"/>
-    <col min="100" max="100" width="10.85546875" customWidth="1"/>
+    <col min="1" max="100" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:100" ht="27" customHeight="1">

--- a/002-board-game-nights/board-game-nights-quote.xlsx
+++ b/002-board-game-nights/board-game-nights-quote.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arut/repo/mscac-event-proposals-2026:27/002-board-game-nights/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C4AB79F-A185-AD43-8EFC-D09C10F549D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14741F2D-A50A-E946-B492-9EFF267FE69E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="500" windowWidth="33360" windowHeight="18760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,13 +125,13 @@
     <t>Non Veg (Mozzarella cheese, bacon, ham, ground beef, pepperoni, mushrooms and Italian hot sausage.)</t>
   </si>
   <si>
-    <t>ARRABBIATA (18")</t>
-  </si>
-  <si>
     <t>https://www.kingslice.ca/menu?location=Bloor+Street+West&amp;menu=pizza</t>
   </si>
   <si>
     <t>https://collegestreet.restaurantsolutions.ca/</t>
+  </si>
+  <si>
+    <t>ARRABBIATA</t>
   </si>
 </sst>
 </file>
@@ -805,7 +805,7 @@
         <v>69.98</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>8</v>
@@ -824,7 +824,7 @@
         <v>84.75</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>28</v>
@@ -952,7 +952,7 @@
         <v>10</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="H4" s="5">
         <v>28.25</v>
